--- a/Evaluation Datasets/argument_extraction_claim_reconstruction_evaluation.xlsx
+++ b/Evaluation Datasets/argument_extraction_claim_reconstruction_evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniluxembourg-my.sharepoint.com/personal/sarah_oberbichler_uni_lu/Documents/Documents/Publikationen/Datasets/Messina/Articles/Argument_Mining/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FF0EDB1-6E24-48DB-A1E0-E7BDE9CDE068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D06B5D07-3916-46A7-921F-05D04A1BE7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -791,7 +791,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -801,12 +801,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -856,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -864,8 +858,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1082,7 +1074,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" width="18.6328125" customWidth="1"/>
-    <col min="9" max="9" width="18.6328125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -1110,7 +1102,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>124</v>
       </c>
     </row>
@@ -1139,7 +1131,7 @@
       <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1168,7 +1160,7 @@
       <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" t="s">
         <v>126</v>
       </c>
     </row>
@@ -1197,7 +1189,7 @@
       <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1226,7 +1218,7 @@
       <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1255,7 +1247,7 @@
       <c r="H6" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1284,7 +1276,7 @@
       <c r="H7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1313,7 +1305,7 @@
       <c r="H8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1342,7 +1334,7 @@
       <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1371,7 +1363,7 @@
       <c r="H10" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1400,7 +1392,7 @@
       <c r="H11" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1429,7 +1421,7 @@
       <c r="H12" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1458,7 +1450,7 @@
       <c r="H13" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1487,7 +1479,7 @@
       <c r="H14" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1516,7 +1508,7 @@
       <c r="H15" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1545,7 +1537,7 @@
       <c r="H16" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1574,7 +1566,7 @@
       <c r="H17" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1603,7 +1595,7 @@
       <c r="H18" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1632,7 +1624,7 @@
       <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" t="s">
         <v>142</v>
       </c>
     </row>
@@ -1661,7 +1653,7 @@
       <c r="H20" t="s">
         <v>41</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" t="s">
         <v>143</v>
       </c>
     </row>
@@ -1690,7 +1682,7 @@
       <c r="H21" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1719,7 +1711,7 @@
       <c r="H22" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" t="s">
         <v>145</v>
       </c>
     </row>
@@ -1748,7 +1740,7 @@
       <c r="H23" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1777,7 +1769,7 @@
       <c r="H24" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1806,7 +1798,7 @@
       <c r="H25" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1835,7 +1827,7 @@
       <c r="H26" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" t="s">
         <v>149</v>
       </c>
     </row>
@@ -1864,7 +1856,7 @@
       <c r="H27" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1893,7 +1885,7 @@
       <c r="H28" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1922,7 +1914,7 @@
       <c r="H29" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1951,7 +1943,7 @@
       <c r="H30" t="s">
         <v>14</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1980,7 +1972,7 @@
       <c r="H31" t="s">
         <v>41</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2009,7 +2001,7 @@
       <c r="H32" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2038,7 +2030,7 @@
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2067,7 +2059,7 @@
       <c r="H34" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2096,7 +2088,7 @@
       <c r="H35" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2125,7 +2117,7 @@
       <c r="H36" t="s">
         <v>14</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2154,7 +2146,7 @@
       <c r="H37" t="s">
         <v>41</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I37" t="s">
         <v>160</v>
       </c>
     </row>
@@ -2183,7 +2175,7 @@
       <c r="H38" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2212,7 +2204,7 @@
       <c r="H39" t="s">
         <v>14</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2241,11 +2233,11 @@
       <c r="H40" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -2270,7 +2262,7 @@
       <c r="H41" t="s">
         <v>16</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2299,7 +2291,7 @@
       <c r="H42" t="s">
         <v>16</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2328,7 +2320,7 @@
       <c r="H43" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2357,7 +2349,7 @@
       <c r="H44" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2386,7 +2378,7 @@
       <c r="H45" t="s">
         <v>14</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="I45" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2415,7 +2407,7 @@
       <c r="H46" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2444,7 +2436,7 @@
       <c r="H47" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2473,7 +2465,7 @@
       <c r="H48" t="s">
         <v>16</v>
       </c>
-      <c r="I48" s="4" t="s">
+      <c r="I48" t="s">
         <v>171</v>
       </c>
     </row>
@@ -2502,7 +2494,7 @@
       <c r="H49" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="4" t="s">
+      <c r="I49" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2531,7 +2523,7 @@
       <c r="H50" t="s">
         <v>16</v>
       </c>
-      <c r="I50" s="4" t="s">
+      <c r="I50" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2560,7 +2552,7 @@
       <c r="H51" t="s">
         <v>14</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="I51" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2589,7 +2581,7 @@
       <c r="H52" t="s">
         <v>14</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="I52" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2618,7 +2610,7 @@
       <c r="H53" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="I53" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2647,7 +2639,7 @@
       <c r="H54" t="s">
         <v>14</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I54" t="s">
         <v>177</v>
       </c>
     </row>
@@ -2676,7 +2668,7 @@
       <c r="H55" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="4" t="s">
+      <c r="I55" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2705,7 +2697,7 @@
       <c r="H56" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="I56" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2734,7 +2726,7 @@
       <c r="H57" t="s">
         <v>14</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="I57" t="s">
         <v>180</v>
       </c>
     </row>
@@ -2763,7 +2755,7 @@
       <c r="H58" t="s">
         <v>14</v>
       </c>
-      <c r="I58" s="4" t="s">
+      <c r="I58" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2792,7 +2784,7 @@
       <c r="H59" t="s">
         <v>16</v>
       </c>
-      <c r="I59" s="4" t="s">
+      <c r="I59" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2821,7 +2813,7 @@
       <c r="H60" t="s">
         <v>14</v>
       </c>
-      <c r="I60" s="4" t="s">
+      <c r="I60" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2850,7 +2842,7 @@
       <c r="H61" t="s">
         <v>41</v>
       </c>
-      <c r="I61" s="4" t="s">
+      <c r="I61" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2879,7 +2871,7 @@
       <c r="H62" t="s">
         <v>14</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I62" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2908,7 +2900,7 @@
       <c r="H63" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2937,7 +2929,7 @@
       <c r="H64" t="s">
         <v>14</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="I64" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2966,7 +2958,7 @@
       <c r="H65" t="s">
         <v>14</v>
       </c>
-      <c r="I65" s="4" t="s">
+      <c r="I65" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2995,17 +2987,11 @@
       <c r="H66" t="s">
         <v>16</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="I66" t="s">
         <v>189</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{445a9c95-0f9d-4953-9db1-bc4a45dd1220}" enabled="0" method="" siteId="{445a9c95-0f9d-4953-9db1-bc4a45dd1220}" removed="1"/>
-</clbl:labelList>
 </file>